--- a/data/trans_orig/P41C_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023</t>
+          <t>Población según si han tenido o tienen dificultades para tener un embarazo en 2023 (tasa de respuesta: 87,29%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>46434</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39758</t>
+          <t>39750</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87415</t>
+          <t>87887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>94,98%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1031,7 +1031,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2554</t>
+          <t>2751</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1495</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>4403</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>10,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3392</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>641400</t>
+          <t>642411</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>668539</t>
+          <t>668193</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>448698</t>
+          <t>448927</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>460782</t>
+          <t>461098</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1098352</t>
+          <t>1098457</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1126910</t>
+          <t>1127480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>5560</t>
+          <t>6301</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>808</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7257</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>1436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9878</t>
+          <t>9787</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1427</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17220</t>
+          <t>17395</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>2991</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11166</t>
+          <t>11279</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6653</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23361</t>
+          <t>23037</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
     </row>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10411</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1318</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10652</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1841,7 +1841,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,97%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11999</t>
+          <t>12228</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1231</t>
+          <t>1332</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7751</t>
+          <t>8205</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,47 +1914,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>8087</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>15924</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>0,26%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>8087</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>3035</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>16205</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,27%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136171</t>
+          <t>136764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153328</t>
+          <t>153281</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159867</t>
+          <t>159649</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173039</t>
+          <t>173146</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,68%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>302463</t>
+          <t>303044</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>323533</t>
+          <t>323422</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,91%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1334</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1130</t>
+          <t>1162</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10889</t>
+          <t>10447</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4160</t>
+          <t>4275</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13850</t>
+          <t>14217</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7334</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19724</t>
+          <t>20236</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2103</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,7 +2473,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6321</t>
+          <t>7158</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1403</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17515</t>
+          <t>16408</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2293</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11121</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6412</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>23206</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,49%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>833040</t>
+          <t>833146</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>868091</t>
+          <t>870021</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,73%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>655429</t>
+          <t>655196</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>674208</t>
+          <t>673870</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1499332</t>
+          <t>1499981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1541674</t>
+          <t>1539397</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,77%</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2894,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6088</t>
+          <t>5797</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1035</t>
+          <t>1058</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6960</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9431</t>
+          <t>9598</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4217</t>
+          <t>4196</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22790</t>
+          <t>22820</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8951</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21715</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15098</t>
+          <t>15405</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>38426</t>
+          <t>39309</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11456</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1180</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12612</t>
+          <t>11074</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,07%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,7%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>3357</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23852</t>
+          <t>23406</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5791</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17091</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10667</t>
+          <t>11249</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>33748</t>
+          <t>35320</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P41C_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P41C_2023-Estudios-trans_orig.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -760,27 +760,27 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>42463</t>
+          <t>49260</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>39750</t>
+          <t>46425</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -795,27 +795,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>90783</t>
+          <t>103502</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87887</t>
+          <t>99554</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>559</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -996,12 +996,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2544</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>559</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>3396</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>4403</t>
+          <t>3635</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>713</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3617</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48320</t>
+          <t>54242</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>43712</t>
+          <t>50531</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>92032</t>
+          <t>104773</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>657094</t>
+          <t>449806</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>642411</t>
+          <t>439363</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>668193</t>
+          <t>456789</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>97,79%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>455879</t>
+          <t>504544</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>448927</t>
+          <t>496879</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>461098</t>
+          <t>509934</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1112973</t>
+          <t>954350</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1098457</t>
+          <t>942862</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1127480</t>
+          <t>963613</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -1520,7 +1520,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6301</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3393</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1422</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7301</t>
+          <t>7954</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>2587</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>9787</t>
+          <t>11858</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,2%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7536</t>
+          <t>7733</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1427</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17395</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5935</t>
+          <t>7551</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2991</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11279</t>
+          <t>14186</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>15285</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>9018</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23037</t>
+          <t>24024</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1756,12 +1756,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10673</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1826,12 +1826,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12228</t>
+          <t>11692</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8205</t>
+          <t>8186</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8317</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>4185</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15924</t>
+          <t>15920</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>673031</t>
+          <t>467135</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>673031</t>
+          <t>467135</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>673031</t>
+          <t>467135</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>519188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>519188</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>468694</t>
+          <t>519188</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1141725</t>
+          <t>986323</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1141725</t>
+          <t>986323</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1141725</t>
+          <t>986323</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>147351</t>
+          <t>161960</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>136764</t>
+          <t>149056</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>153281</t>
+          <t>168037</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,07%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>167499</t>
+          <t>188024</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>159649</t>
+          <t>180202</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>173146</t>
+          <t>194404</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>91,59%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>95,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>314850</t>
+          <t>349984</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>303044</t>
+          <t>336741</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>323422</t>
+          <t>359322</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>88,93%</t>
+          <t>89,31%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4439</t>
+          <t>4393</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1162</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10447</t>
+          <t>10671</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8181</t>
+          <t>8387</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4275</t>
+          <t>4345</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>14217</t>
+          <t>14958</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>12621</t>
+          <t>12780</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7334</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>20236</t>
+          <t>21110</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2463,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6684</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7158</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -2523,7 +2523,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>6115</t>
+          <t>6834</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1612</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16408</t>
+          <t>20854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5469</t>
+          <t>5711</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2293</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>12140</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>11584</t>
+          <t>12545</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>6346</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22115</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>173187</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>173187</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157906</t>
+          <t>173187</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>182873</t>
+          <t>203878</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>182873</t>
+          <t>203878</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182873</t>
+          <t>203878</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>340778</t>
+          <t>377065</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>340778</t>
+          <t>377065</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>340778</t>
+          <t>377065</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>852766</t>
+          <t>666008</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>833146</t>
+          <t>650198</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>870021</t>
+          <t>676233</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>665842</t>
+          <t>741827</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>655196</t>
+          <t>731327</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>673870</t>
+          <t>750506</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1518606</t>
+          <t>1407836</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1499981</t>
+          <t>1388223</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1539397</t>
+          <t>1421527</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>96,45%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>96,82%</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1208</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>5797</t>
+          <t>7951</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>7932</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>3225</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>1058</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>6960</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>4433</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>9598</t>
+          <t>12177</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>11975</t>
+          <t>12127</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>4196</t>
+          <t>6237</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22820</t>
+          <t>20392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>14668</t>
+          <t>16497</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>10828</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>21715</t>
+          <t>24563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>26643</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>15405</t>
+          <t>19693</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>39350</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2761</t>
+          <t>2719</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>8438</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>6077</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4475</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11074</t>
+          <t>11352</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,77%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>10548</t>
+          <t>11451</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>5474</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>23406</t>
+          <t>25546</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t>10124</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5791</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17670</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>20368</t>
+          <t>21575</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>11249</t>
+          <t>12910</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>35320</t>
+          <t>37646</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,56%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>879257</t>
+          <t>694564</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>879257</t>
+          <t>694564</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>879257</t>
+          <t>694564</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>695279</t>
+          <t>773596</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1574535</t>
+          <t>1468161</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1574535</t>
+          <t>1468161</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1574535</t>
+          <t>1468161</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
